--- a/output/Data and Chart Outputs/vietnam_gas.xlsx
+++ b/output/Data and Chart Outputs/vietnam_gas.xlsx
@@ -156,6 +156,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Vietnam natural gas production (NSO) (to Sep/26)</a:t>
             </a:r>
           </a:p>
@@ -1436,7 +1437,7 @@
         <v>44958</v>
       </c>
       <c r="B93" t="n">
-        <v>23.538</v>
+        <v>23.537</v>
       </c>
     </row>
     <row r="94">
@@ -4590,7 +4591,7 @@
         <v>659.05</v>
       </c>
       <c r="C97" t="n">
-        <v>23.538</v>
+        <v>23.537</v>
       </c>
       <c r="D97" t="n">
         <v>66.41</v>
